--- a/myapp/files/80_distances/weighted_pValue_Risks.xlsx
+++ b/myapp/files/80_distances/weighted_pValue_Risks.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t xml:space="preserve">scenario</t>
   </si>
@@ -30,36 +30,6 @@
   </si>
   <si>
     <t xml:space="preserve">pValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMPACT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">classic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weighted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OCCURRENCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">centertogrid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reachedgrid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pooling</t>
   </si>
 </sst>
 </file>
@@ -408,222 +378,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2"/>
-      <c r="F2" t="n">
-        <v>0.000000193488823593316</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3"/>
-      <c r="F3" t="n">
-        <v>0.000016240824769113</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4"/>
-      <c r="F4" t="n">
-        <v>0.00100060498288918</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5"/>
-      <c r="F5" t="n">
-        <v>0.000933314364487298</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6"/>
-      <c r="F6" t="n">
-        <v>0.00109598311472131</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7"/>
-      <c r="F7" t="n">
-        <v>0.00138594899019165</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8"/>
-      <c r="F8" t="n">
-        <v>0.0000846158081204502</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9"/>
-      <c r="F9" t="n">
-        <v>0.0000883419088190211</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10"/>
-      <c r="F10" t="n">
-        <v>0.000077512602359692</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11"/>
-      <c r="F11" t="n">
-        <v>0.0000671346952448423</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12"/>
-      <c r="F12" t="n">
-        <v>0.00000000000000000023756281353499</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13"/>
-      <c r="F13" t="n">
-        <v>0.0000000000000000000427194204480146</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
